--- a/TEXT FUNCTION.xlsx
+++ b/TEXT FUNCTION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucky\Desktop\Advance Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94911B7-2D26-4C96-A742-52CF8DEAEB13}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C074C339-C10A-49C0-B46B-B5F31E76E328}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{EE5EAFF9-E59F-4339-9304-4ECF4C8B90F1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -88,6 +88,30 @@
   </si>
   <si>
     <t>NAME</t>
+  </si>
+  <si>
+    <t>lokesh</t>
+  </si>
+  <si>
+    <t>nishan</t>
+  </si>
+  <si>
+    <t>gaurav</t>
+  </si>
+  <si>
+    <t>dipak</t>
+  </si>
+  <si>
+    <t>ahire</t>
+  </si>
+  <si>
+    <t>aher</t>
+  </si>
+  <si>
+    <t>deore</t>
+  </si>
+  <si>
+    <t>kuwar</t>
   </si>
 </sst>
 </file>
@@ -736,60 +760,132 @@
       <c r="B12" t="s">
         <v>14</v>
       </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>17</v>
       </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>1</v>
       </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>2</v>
       </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
